--- a/InputData/elec/RQSD/RPS Qualifying Source Definitions.xlsx
+++ b/InputData/elec/RQSD/RPS Qualifying Source Definitions.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26731"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="26924"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Olivia Ashmoore\Documents\EPS_Models by Region\RMI\RMI_all_states\template_state_3.3\elec\RQSD\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Olivia Ashmoore\Documents\EPS_Models by Region\RMI\RMI_all_states\AL\elec\RQSD\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5F602536-1F95-49D4-970C-7E68BEDC8539}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{3667A9B6-940F-4DEB-A703-6829545F8ACC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1440" yWindow="1440" windowWidth="14400" windowHeight="7455" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="360" yWindow="360" windowWidth="14400" windowHeight="7290" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,6 @@
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
         <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -37,127 +36,127 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="41">
   <si>
+    <t>Source:</t>
+  </si>
+  <si>
+    <t>Each U.S. state that has an RPS defines the sources that qualify for that RPS, leading to</t>
+  </si>
+  <si>
+    <t>Electricity Source</t>
+  </si>
+  <si>
+    <t>nuclear</t>
+  </si>
+  <si>
+    <t>hydro</t>
+  </si>
+  <si>
+    <t>solar PV</t>
+  </si>
+  <si>
+    <t>solar thermal</t>
+  </si>
+  <si>
+    <t>biomass</t>
+  </si>
+  <si>
+    <t>geothermal</t>
+  </si>
+  <si>
+    <t>petroleum</t>
+  </si>
+  <si>
+    <t>natural gas peaker</t>
+  </si>
+  <si>
+    <t>Notes</t>
+  </si>
+  <si>
+    <t>The non-BAU version of this variable supports a boolean policy lever and is intended to be set by the</t>
+  </si>
+  <si>
     <t>RQSD BAU RPS Qualifying Source Definitions</t>
   </si>
   <si>
+    <t>RQSD RPS Qualifying Source Definitions</t>
+  </si>
+  <si>
+    <t>lignite</t>
+  </si>
+  <si>
+    <t>hard coal</t>
+  </si>
+  <si>
+    <t>onshore wind</t>
+  </si>
+  <si>
+    <t>offshore wind</t>
+  </si>
+  <si>
+    <t>differences between states.  Here, we use a "clean energy standard"</t>
+  </si>
+  <si>
+    <t>(counting everything except fossil fuels) as our definition for the BAU case.</t>
+  </si>
+  <si>
+    <t>model user.  The example we include uses only wind, solar, and geothermal.</t>
+  </si>
+  <si>
+    <t>Hydro is excluded because of limited potential for new large hydro and land use impacts.</t>
+  </si>
+  <si>
+    <t>Biomass is excluded because it is not truly carbon-neutral, and it has other issues, such as</t>
+  </si>
+  <si>
+    <t>local air quality impacts and land use challenges.</t>
+  </si>
+  <si>
+    <t>Nuclear is excluded because of the need to manage nuclear waste.</t>
+  </si>
+  <si>
+    <t>see notes</t>
+  </si>
+  <si>
+    <t>crude oil</t>
+  </si>
+  <si>
+    <t>heavy or residual fuel oil</t>
+  </si>
+  <si>
+    <t>municipal solid waste</t>
+  </si>
+  <si>
+    <t>Qualifies for RPS (Boolean)</t>
+  </si>
+  <si>
+    <t>natural gas steam turbine</t>
+  </si>
+  <si>
+    <t>natural gas combined cycle</t>
+  </si>
+  <si>
+    <t>hard coal w CCS</t>
+  </si>
+  <si>
+    <t>natural gas combined cycle w CCS</t>
+  </si>
+  <si>
+    <t>biomass w CCS</t>
+  </si>
+  <si>
+    <t>lignite w CCS</t>
+  </si>
+  <si>
+    <t>small modular reactor</t>
+  </si>
+  <si>
+    <t>hydrogen combustion turbine</t>
+  </si>
+  <si>
+    <t>hydrogen combined cycle</t>
+  </si>
+  <si>
     <t>Alabama</t>
-  </si>
-  <si>
-    <t>RQSD RPS Qualifying Source Definitions</t>
-  </si>
-  <si>
-    <t>Source:</t>
-  </si>
-  <si>
-    <t>see notes</t>
-  </si>
-  <si>
-    <t>Notes</t>
-  </si>
-  <si>
-    <t>Each U.S. state that has an RPS defines the sources that qualify for that RPS, leading to</t>
-  </si>
-  <si>
-    <t>differences between states.  Here, we use a "clean energy standard"</t>
-  </si>
-  <si>
-    <t>(counting everything except fossil fuels) as our definition for the BAU case.</t>
-  </si>
-  <si>
-    <t>The non-BAU version of this variable supports a boolean policy lever and is intended to be set by the</t>
-  </si>
-  <si>
-    <t>model user.  The example we include uses only wind, solar, and geothermal.</t>
-  </si>
-  <si>
-    <t>Hydro is excluded because of limited potential for new large hydro and land use impacts.</t>
-  </si>
-  <si>
-    <t>Biomass is excluded because it is not truly carbon-neutral, and it has other issues, such as</t>
-  </si>
-  <si>
-    <t>local air quality impacts and land use challenges.</t>
-  </si>
-  <si>
-    <t>Nuclear is excluded because of the need to manage nuclear waste.</t>
-  </si>
-  <si>
-    <t>Electricity Source</t>
-  </si>
-  <si>
-    <t>Qualifies for RPS (Boolean)</t>
-  </si>
-  <si>
-    <t>hard coal</t>
-  </si>
-  <si>
-    <t>natural gas steam turbine</t>
-  </si>
-  <si>
-    <t>natural gas combined cycle</t>
-  </si>
-  <si>
-    <t>nuclear</t>
-  </si>
-  <si>
-    <t>hydro</t>
-  </si>
-  <si>
-    <t>onshore wind</t>
-  </si>
-  <si>
-    <t>solar PV</t>
-  </si>
-  <si>
-    <t>solar thermal</t>
-  </si>
-  <si>
-    <t>biomass</t>
-  </si>
-  <si>
-    <t>geothermal</t>
-  </si>
-  <si>
-    <t>petroleum</t>
-  </si>
-  <si>
-    <t>natural gas peaker</t>
-  </si>
-  <si>
-    <t>lignite</t>
-  </si>
-  <si>
-    <t>offshore wind</t>
-  </si>
-  <si>
-    <t>crude oil</t>
-  </si>
-  <si>
-    <t>heavy or residual fuel oil</t>
-  </si>
-  <si>
-    <t>municipal solid waste</t>
-  </si>
-  <si>
-    <t>hard coal w CCS</t>
-  </si>
-  <si>
-    <t>natural gas combined cycle w CCS</t>
-  </si>
-  <si>
-    <t>biomass w CCS</t>
-  </si>
-  <si>
-    <t>lignite w CCS</t>
-  </si>
-  <si>
-    <t>small modular reactor</t>
-  </si>
-  <si>
-    <t>hydrogen combustion turbine</t>
-  </si>
-  <si>
-    <t>hydrogen combined cycle</t>
   </si>
 </sst>
 </file>
@@ -215,7 +214,7 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
   <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
@@ -541,26 +540,26 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.75">
       <c r="A1" s="1" t="s">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="B1" t="s">
-        <v>1</v>
+        <v>40</v>
       </c>
       <c r="C1" s="5">
-        <v>45194</v>
+        <v>45237</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.75">
       <c r="A2" s="1" t="s">
-        <v>2</v>
+        <v>14</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.75">
       <c r="A4" s="1" t="s">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="B4" t="s">
-        <v>4</v>
+        <v>26</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.75">
@@ -568,57 +567,57 @@
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.75">
       <c r="A8" s="1" t="s">
-        <v>5</v>
+        <v>11</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.75">
       <c r="A9" t="s">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.75">
       <c r="A10" t="s">
-        <v>7</v>
+        <v>19</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.75">
       <c r="A11" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.75">
       <c r="A13" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.75">
       <c r="A14" t="s">
-        <v>10</v>
+        <v>21</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.75">
       <c r="A15" t="s">
-        <v>11</v>
+        <v>22</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.75">
       <c r="A16" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.75">
       <c r="A17" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.75">
       <c r="A18" t="s">
-        <v>14</v>
+        <v>25</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="1200" verticalDpi="1200"/>
+  <pageSetup orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -636,15 +635,15 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.75">
       <c r="A1" s="1" t="s">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>16</v>
+        <v>30</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.75">
       <c r="A2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B2">
         <v>0</v>
@@ -652,7 +651,7 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.75">
       <c r="A3" t="s">
-        <v>18</v>
+        <v>31</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -660,7 +659,7 @@
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.75">
       <c r="A4" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -668,7 +667,7 @@
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.75">
       <c r="A5" t="s">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="B5">
         <v>1</v>
@@ -676,7 +675,7 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.75">
       <c r="A6" t="s">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="B6">
         <v>1</v>
@@ -684,7 +683,7 @@
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.75">
       <c r="A7" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="B7">
         <v>1</v>
@@ -692,7 +691,7 @@
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.75">
       <c r="A8" t="s">
-        <v>23</v>
+        <v>5</v>
       </c>
       <c r="B8">
         <v>1</v>
@@ -700,7 +699,7 @@
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.75">
       <c r="A9" t="s">
-        <v>24</v>
+        <v>6</v>
       </c>
       <c r="B9">
         <v>1</v>
@@ -708,7 +707,7 @@
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.75">
       <c r="A10" t="s">
-        <v>25</v>
+        <v>7</v>
       </c>
       <c r="B10">
         <v>1</v>
@@ -716,7 +715,7 @@
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.75">
       <c r="A11" t="s">
-        <v>26</v>
+        <v>8</v>
       </c>
       <c r="B11">
         <v>1</v>
@@ -724,7 +723,7 @@
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.75">
       <c r="A12" t="s">
-        <v>27</v>
+        <v>9</v>
       </c>
       <c r="B12">
         <v>0</v>
@@ -732,7 +731,7 @@
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.75">
       <c r="A13" t="s">
-        <v>28</v>
+        <v>10</v>
       </c>
       <c r="B13">
         <v>0</v>
@@ -740,7 +739,7 @@
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.75">
       <c r="A14" t="s">
-        <v>29</v>
+        <v>15</v>
       </c>
       <c r="B14">
         <f>B2</f>
@@ -749,7 +748,7 @@
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.75">
       <c r="A15" t="s">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="B15">
         <v>1</v>
@@ -757,7 +756,7 @@
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.75">
       <c r="A16" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="B16">
         <v>0</v>
@@ -765,7 +764,7 @@
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.75">
       <c r="A17" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="B17">
         <v>0</v>
@@ -773,7 +772,7 @@
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.75">
       <c r="A18" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="B18">
         <v>0</v>
@@ -781,7 +780,7 @@
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.75">
       <c r="A19" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B19">
         <v>1</v>
@@ -789,7 +788,7 @@
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.75">
       <c r="A20" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B20">
         <v>1</v>
@@ -797,7 +796,7 @@
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.75">
       <c r="A21" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B21">
         <v>1</v>
@@ -805,7 +804,7 @@
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.75">
       <c r="A22" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B22">
         <v>1</v>
@@ -813,7 +812,7 @@
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.75">
       <c r="A23" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B23">
         <v>1</v>
@@ -821,7 +820,7 @@
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.75">
       <c r="A24" s="4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B24">
         <v>1</v>
@@ -829,7 +828,7 @@
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.75">
       <c r="A25" s="4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B25">
         <v>1</v>
@@ -854,15 +853,15 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.75">
       <c r="A1" s="1" t="s">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>16</v>
+        <v>30</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.75">
       <c r="A2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B2">
         <v>0</v>
@@ -870,7 +869,7 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.75">
       <c r="A3" t="s">
-        <v>18</v>
+        <v>31</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -878,7 +877,7 @@
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.75">
       <c r="A4" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -886,7 +885,7 @@
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.75">
       <c r="A5" t="s">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -894,7 +893,7 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.75">
       <c r="A6" t="s">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="B6">
         <v>0</v>
@@ -902,7 +901,7 @@
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.75">
       <c r="A7" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="B7">
         <v>1</v>
@@ -910,7 +909,7 @@
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.75">
       <c r="A8" t="s">
-        <v>23</v>
+        <v>5</v>
       </c>
       <c r="B8">
         <v>1</v>
@@ -918,7 +917,7 @@
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.75">
       <c r="A9" t="s">
-        <v>24</v>
+        <v>6</v>
       </c>
       <c r="B9">
         <v>1</v>
@@ -926,7 +925,7 @@
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.75">
       <c r="A10" t="s">
-        <v>25</v>
+        <v>7</v>
       </c>
       <c r="B10">
         <v>0</v>
@@ -934,7 +933,7 @@
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.75">
       <c r="A11" t="s">
-        <v>26</v>
+        <v>8</v>
       </c>
       <c r="B11">
         <v>1</v>
@@ -942,7 +941,7 @@
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.75">
       <c r="A12" t="s">
-        <v>27</v>
+        <v>9</v>
       </c>
       <c r="B12">
         <v>0</v>
@@ -950,7 +949,7 @@
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.75">
       <c r="A13" t="s">
-        <v>28</v>
+        <v>10</v>
       </c>
       <c r="B13">
         <v>0</v>
@@ -958,7 +957,7 @@
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.75">
       <c r="A14" t="s">
-        <v>29</v>
+        <v>15</v>
       </c>
       <c r="B14">
         <f>B2</f>
@@ -967,7 +966,7 @@
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.75">
       <c r="A15" t="s">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="B15">
         <v>1</v>
@@ -975,7 +974,7 @@
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.75">
       <c r="A16" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="B16">
         <v>0</v>
@@ -983,7 +982,7 @@
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.75">
       <c r="A17" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="B17">
         <v>0</v>
@@ -991,7 +990,7 @@
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.75">
       <c r="A18" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="B18">
         <v>0</v>
@@ -999,7 +998,7 @@
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.75">
       <c r="A19" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B19">
         <v>0</v>
@@ -1007,7 +1006,7 @@
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.75">
       <c r="A20" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B20">
         <v>0</v>
@@ -1015,7 +1014,7 @@
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.75">
       <c r="A21" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B21">
         <v>0</v>
@@ -1023,7 +1022,7 @@
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.75">
       <c r="A22" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B22">
         <v>0</v>
@@ -1031,7 +1030,7 @@
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.75">
       <c r="A23" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B23">
         <v>0</v>
@@ -1039,7 +1038,7 @@
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.75">
       <c r="A24" s="4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B24">
         <v>1</v>
@@ -1047,7 +1046,7 @@
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.75">
       <c r="A25" s="4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B25">
         <v>1</v>

--- a/InputData/elec/RQSD/RPS Qualifying Source Definitions.xlsx
+++ b/InputData/elec/RQSD/RPS Qualifying Source Definitions.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Olivia Ashmoore\Documents\EPS_Models by Region\RMI\RMI_all_states\AL\elec\RQSD\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Olivia Ashmoore\Documents\EPS_Models by Region\RMI\RMI_all_states\AZ\elec\RQSD\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{3667A9B6-940F-4DEB-A703-6829545F8ACC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{A1C1883F-7E71-4FCA-A921-F770E15A1675}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="360" yWindow="360" windowWidth="14400" windowHeight="7290" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -156,7 +156,7 @@
     <t>hydrogen combined cycle</t>
   </si>
   <si>
-    <t>Alabama</t>
+    <t>Arizona</t>
   </si>
 </sst>
 </file>

--- a/InputData/elec/RQSD/RPS Qualifying Source Definitions.xlsx
+++ b/InputData/elec/RQSD/RPS Qualifying Source Definitions.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="26924"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27126"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Olivia Ashmoore\Documents\EPS_Models by Region\RMI\RMI_all_states\AZ\elec\RQSD\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Olivia Ashmoore\Documents\EPS_Models by Region\RMI\RMI_all_states\AL\elec\RQSD\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{A1C1883F-7E71-4FCA-A921-F770E15A1675}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{74831CFC-AB8F-463B-9DFE-53867396931B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="360" yWindow="360" windowWidth="14400" windowHeight="7290" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="12195" yWindow="225" windowWidth="16605" windowHeight="17055" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
@@ -156,7 +156,7 @@
     <t>hydrogen combined cycle</t>
   </si>
   <si>
-    <t>Arizona</t>
+    <t>Alabama</t>
   </si>
 </sst>
 </file>
@@ -533,12 +533,12 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:C18"/>
-  <sheetFormatPr defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="84.54296875" customWidth="1"/>
+    <col min="2" max="2" width="84.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.75">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>13</v>
       </c>
@@ -546,15 +546,15 @@
         <v>40</v>
       </c>
       <c r="C1" s="5">
-        <v>45237</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.75">
+        <v>45302</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.75">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>0</v>
       </c>
@@ -562,55 +562,55 @@
         <v>26</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.75">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B5" s="2"/>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.75">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.75">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.75">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.75">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.75">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.75">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.75">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.75">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.75">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.75">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>25</v>
       </c>
@@ -627,13 +627,13 @@
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:B25"/>
-  <sheetFormatPr defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="25.40625" customWidth="1"/>
-    <col min="2" max="2" width="28.40625" customWidth="1"/>
+    <col min="1" max="1" width="25.42578125" customWidth="1"/>
+    <col min="2" max="2" width="28.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>2</v>
       </c>
@@ -641,7 +641,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>16</v>
       </c>
@@ -649,7 +649,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>31</v>
       </c>
@@ -657,7 +657,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>32</v>
       </c>
@@ -665,23 +665,23 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>3</v>
       </c>
       <c r="B5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.75">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>4</v>
       </c>
       <c r="B6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.75">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>17</v>
       </c>
@@ -689,7 +689,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>5</v>
       </c>
@@ -697,7 +697,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>6</v>
       </c>
@@ -705,7 +705,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>7</v>
       </c>
@@ -713,7 +713,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>8</v>
       </c>
@@ -721,7 +721,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>9</v>
       </c>
@@ -729,7 +729,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>10</v>
       </c>
@@ -737,7 +737,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>15</v>
       </c>
@@ -746,7 +746,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>18</v>
       </c>
@@ -754,7 +754,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>27</v>
       </c>
@@ -762,7 +762,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>28</v>
       </c>
@@ -770,7 +770,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>29</v>
       </c>
@@ -778,7 +778,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>33</v>
       </c>
@@ -786,7 +786,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>34</v>
       </c>
@@ -794,7 +794,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>35</v>
       </c>
@@ -802,7 +802,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>36</v>
       </c>
@@ -810,7 +810,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>37</v>
       </c>
@@ -818,7 +818,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
         <v>38</v>
       </c>
@@ -826,7 +826,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25" s="4" t="s">
         <v>39</v>
       </c>
@@ -845,13 +845,13 @@
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:B25"/>
-  <sheetFormatPr defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="25.40625" customWidth="1"/>
-    <col min="2" max="2" width="28.40625" customWidth="1"/>
+    <col min="1" max="1" width="25.42578125" customWidth="1"/>
+    <col min="2" max="2" width="28.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>2</v>
       </c>
@@ -859,7 +859,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>16</v>
       </c>
@@ -867,7 +867,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>31</v>
       </c>
@@ -875,7 +875,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>32</v>
       </c>
@@ -883,7 +883,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -891,7 +891,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>4</v>
       </c>
@@ -899,7 +899,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>17</v>
       </c>
@@ -907,7 +907,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>5</v>
       </c>
@@ -915,7 +915,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>6</v>
       </c>
@@ -923,7 +923,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>7</v>
       </c>
@@ -931,7 +931,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>8</v>
       </c>
@@ -939,7 +939,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>9</v>
       </c>
@@ -947,7 +947,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>10</v>
       </c>
@@ -955,7 +955,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>15</v>
       </c>
@@ -964,7 +964,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>18</v>
       </c>
@@ -972,7 +972,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>27</v>
       </c>
@@ -980,7 +980,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>28</v>
       </c>
@@ -988,7 +988,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>29</v>
       </c>
@@ -996,7 +996,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>33</v>
       </c>
@@ -1004,7 +1004,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>34</v>
       </c>
@@ -1012,7 +1012,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>35</v>
       </c>
@@ -1020,7 +1020,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>36</v>
       </c>
@@ -1028,7 +1028,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>37</v>
       </c>
@@ -1036,7 +1036,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
         <v>38</v>
       </c>
@@ -1044,7 +1044,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25" s="4" t="s">
         <v>39</v>
       </c>
